--- a/excel/hmd_Continuous.xlsx
+++ b/excel/hmd_Continuous.xlsx
@@ -1,50 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hamilton\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93560E78-A801-4049-A729-5BBDE7D93E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6CE0FD-ACC1-4B7E-A6C2-1E5816E468A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="723" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10155" yWindow="2820" windowWidth="18285" windowHeight="12375" tabRatio="723" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tri3_均布_8-64" sheetId="1" r:id="rId1"/>
-    <sheet name="Tri3_非均布_4-64" sheetId="2" r:id="rId2"/>
-    <sheet name="拉伸均布_4-64" sheetId="3" r:id="rId3"/>
-    <sheet name="压缩均布_4-64" sheetId="4" r:id="rId4"/>
-    <sheet name="拉伸非均布_4-64" sheetId="5" r:id="rId5"/>
-    <sheet name="压缩非均布_4-64" sheetId="6" r:id="rId6"/>
-    <sheet name="Tri6拉伸非均布_4-64" sheetId="7" r:id="rId7"/>
-    <sheet name="Tri6压缩非均布_4-64" sheetId="8" r:id="rId8"/>
+    <sheet name="Tri3_均布_4-32" sheetId="1" r:id="rId1"/>
+    <sheet name="Tri6_均布_4-32" sheetId="9" r:id="rId2"/>
+    <sheet name="Tri3_非均布_4-32" sheetId="2" r:id="rId3"/>
+    <sheet name="Tri6_非均布_4-32" sheetId="3" r:id="rId4"/>
+    <sheet name="压缩均布_4-64" sheetId="4" r:id="rId5"/>
+    <sheet name="拉伸非均布_4-64" sheetId="5" r:id="rId6"/>
+    <sheet name="压缩非均布_4-64" sheetId="6" r:id="rId7"/>
+    <sheet name="Tri6拉伸非均布_4-64" sheetId="7" r:id="rId8"/>
+    <sheet name="Tri6压缩非均布_4-64" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="4">
-  <si>
-    <t>没稀疏矩阵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>L2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1">
   <si>
     <t>`</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -372,67 +364,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A2:G6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" dyDescent="0.2">
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
     <row r="2" spans="1:7" dyDescent="0.2">
       <c r="A2">
-        <v>-0.3010299956639812</v>
+        <v>-1.3979400086720375</v>
       </c>
       <c r="B2">
-        <v>-0.83418302315598081</v>
+        <v>-0.52827875903705213</v>
       </c>
       <c r="C2">
-        <v>-1.6525793166363008</v>
+        <v>-0.5280239360864619</v>
       </c>
       <c r="G2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" dyDescent="0.2">
       <c r="A3">
-        <v>-0.6020599913279624</v>
+        <v>-1.6989700043360187</v>
       </c>
       <c r="B3">
-        <v>-1.1364818515483281</v>
+        <v>-0.83418302315598081</v>
       </c>
       <c r="C3">
-        <v>-2.25457879976442</v>
+        <v>-1.1182806001342012</v>
       </c>
     </row>
     <row r="4" spans="1:7" dyDescent="0.2">
       <c r="A4">
-        <v>-0.90308998699194354</v>
+        <v>-2.0</v>
       </c>
       <c r="B4">
-        <v>-1.4378311882546349</v>
+        <v>-1.1364818515483281</v>
       </c>
       <c r="C4">
-        <v>-2.8566212096692922</v>
+        <v>-1.7178164371388822</v>
       </c>
     </row>
     <row r="5" spans="1:7" dyDescent="0.2">
       <c r="A5">
-        <v>-1.2041199826559248</v>
+        <v>-2.3010299956639813</v>
       </c>
       <c r="B5">
-        <v>-1.7389410944633268</v>
+        <v>-1.4378311882546349</v>
       </c>
       <c r="C5">
-        <v>-3.4586640617285438</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" dyDescent="0.2">
-      <c r="D9" t="s">
-        <v>0</v>
+        <v>-2.3192741032639916</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>-2.6020599913279625</v>
+      </c>
+      <c r="C6">
+        <v>-2.9211853408805246</v>
       </c>
     </row>
   </sheetData>
@@ -443,64 +430,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D97A7BB-3136-4DE9-9F43-FA45C9D5B719}">
-  <dimension ref="A2:D8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9883820C-9A25-4344-B8B3-EEB49CC6CC54}">
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:4" dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="B2">
-        <v>-0.88435027713528391</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" dyDescent="0.2">
+        <v>-1.3523482187057363</v>
+      </c>
+      <c r="C2">
+        <v>-2.077517765522604</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>-0.3010299956639812</v>
       </c>
       <c r="B3">
-        <v>-0.97134317213308052</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" dyDescent="0.2">
+        <v>-1.9480103913857063</v>
+      </c>
+      <c r="C3">
+        <v>-2.963731173781501</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>-0.6020599913279624</v>
       </c>
       <c r="B4">
-        <v>-1.6599478629503444</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" dyDescent="0.2">
+        <v>-2.5488697522325716</v>
+      </c>
+      <c r="C4">
+        <v>-3.8623288872441885</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
-        <v>-0.90308998699194354</v>
+        <v>-0.9030899869919435</v>
       </c>
       <c r="B5">
-        <v>-1.494482032409113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" dyDescent="0.2">
-      <c r="A6">
-        <v>-1.2041199826559248</v>
-      </c>
-      <c r="B6">
-        <v>-2.3489617033838268</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" dyDescent="0.2">
-      <c r="D8" t="s">
-        <v>0</v>
+        <v>-3.1508174648706673</v>
+      </c>
+      <c r="C5">
+        <v>-4.7643760187149775</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95D2A0D4-1E12-4220-9F05-F78D2D8FDE8A}">
-  <dimension ref="A2:C6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D97A7BB-3136-4DE9-9F43-FA45C9D5B719}">
+  <dimension ref="A2:C5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="1:3" dyDescent="0.2">
@@ -508,10 +495,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>-0.70225948103269897</v>
+        <v>-0.38103137756065719</v>
       </c>
       <c r="C2">
-        <v>-1.2454752245501006</v>
+        <v>-0.86915963672595342</v>
       </c>
     </row>
     <row r="3" spans="1:3" dyDescent="0.2">
@@ -519,10 +506,10 @@
         <v>-0.3010299956639812</v>
       </c>
       <c r="B3">
-        <v>-1.0138434808378871</v>
+        <v>-0.25748526761298429</v>
       </c>
       <c r="C3">
-        <v>-1.8559757919327553</v>
+        <v>-0.97900471883945051</v>
       </c>
     </row>
     <row r="4" spans="1:3" dyDescent="0.2">
@@ -530,10 +517,10 @@
         <v>-0.6020599913279624</v>
       </c>
       <c r="B4">
-        <v>-1.3175124553039688</v>
+        <v>-0.62560543168159033</v>
       </c>
       <c r="C4">
-        <v>-2.4600399026875786</v>
+        <v>-1.6543907596313943</v>
       </c>
     </row>
     <row r="5" spans="1:3" dyDescent="0.2">
@@ -541,21 +528,65 @@
         <v>-0.90308998699194354</v>
       </c>
       <c r="B5">
-        <v>-1.6192013469655313</v>
+        <v>-0.11842759159754823</v>
       </c>
       <c r="C5">
-        <v>-3.0625656143360174</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" dyDescent="0.2">
-      <c r="A6">
-        <v>-1.2041199826559248</v>
-      </c>
-      <c r="B6">
-        <v>-1.920395985494602</v>
-      </c>
-      <c r="C6">
-        <v>-3.6646633461346232</v>
+        <v>-1.4887222073526105</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95D2A0D4-1E12-4220-9F05-F78D2D8FDE8A}">
+  <dimension ref="A2:C5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="1:3" dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>-0.53511638500034131</v>
+      </c>
+      <c r="C2">
+        <v>-1.2711773184393043</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" dyDescent="0.2">
+      <c r="A3">
+        <v>-0.3010299956639812</v>
+      </c>
+      <c r="B3">
+        <v>-1.5387496472400417</v>
+      </c>
+      <c r="C3">
+        <v>-2.5932517057475852</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" dyDescent="0.2">
+      <c r="A4">
+        <v>-0.6020599913279624</v>
+      </c>
+      <c r="B4">
+        <v>-1.0024595832805596</v>
+      </c>
+      <c r="C4">
+        <v>-2.3813627365333065</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" dyDescent="0.2">
+      <c r="A5">
+        <v>-0.90308998699194354</v>
+      </c>
+      <c r="B5">
+        <v>-1.8216982142340998</v>
+      </c>
+      <c r="C5">
+        <v>-3.4909331746806629</v>
       </c>
     </row>
   </sheetData>
@@ -565,7 +596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D074C53-3C70-42BE-BAED-F014663172DD}">
   <dimension ref="A2:C6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -631,7 +662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176EF82D-EF43-40AF-BC88-FBCB12902290}">
   <dimension ref="A2:C6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -698,7 +729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{047244F3-0B4C-40B4-9DAC-A838A8D8CB65}">
   <dimension ref="A2:C6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -764,28 +795,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31A03B73-3A87-423C-984B-AC3339D1505B}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A2:C5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" dyDescent="0.2">
       <c r="A2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>-0.6817782828505373</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>-0.68177828285053732</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" dyDescent="0.2">
       <c r="A3">
         <v>-0.3010299956639812</v>
       </c>
       <c r="C3">
-        <v>-1.526340418561165</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>-1.5263404185611651</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" dyDescent="0.2">
       <c r="A4">
         <v>-0.6020599913279624</v>
       </c>
@@ -793,9 +824,9 @@
         <v>-1.9227670125162188</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" dyDescent="0.2">
       <c r="A5">
-        <v>-0.9030899869919435</v>
+        <v>-0.90308998699194354</v>
       </c>
       <c r="C5">
         <v>-3.2859218825567122</v>
@@ -808,28 +839,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7DC4FF5-AB9C-4E25-9AA5-877098EDA9EE}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A2:C6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" dyDescent="0.2">
       <c r="A2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>-0.3630016461723619</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>-0.36300164617236191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" dyDescent="0.2">
       <c r="A3">
         <v>-0.3010299956639812</v>
       </c>
       <c r="C3">
-        <v>-2.184234300000076</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>-2.1842343000000759</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" dyDescent="0.2">
       <c r="A4">
         <v>-0.6020599913279624</v>
       </c>
@@ -837,20 +868,20 @@
         <v>-1.8951345700779734</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" dyDescent="0.2">
       <c r="A5">
-        <v>-0.9030899869919435</v>
+        <v>-0.90308998699194354</v>
       </c>
       <c r="C5">
         <v>-3.2718795746073814</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" dyDescent="0.2">
       <c r="A6">
         <v>-1.2041199826559248</v>
       </c>
       <c r="C6">
-        <v>-2.656231668151022</v>
+        <v>-2.6562316681510221</v>
       </c>
     </row>
   </sheetData>
